--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_Inputs_BRD-06_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_Inputs_BRD-06_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -28,7 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Start here'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Documents and print formats'!$A$12:$K$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Documents and print formats'!$12:$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'E-mail wordings'!$A$12:$K$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'E-mail wordings'!$A$12:$K$58</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'E-mail wordings'!$12:$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Schedules and timings'!$A$12:$K$24</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Schedules and timings'!$12:$12</definedName>
@@ -816,7 +816,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="D23" s="14" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>34 items</t>
+          <t>45 items</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="F6" s="24" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="G6" s="24">
         <f>COUNTIF('E-mail wordings'!K:K,"Open")</f>
@@ -9819,7 +9819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -11996,47 +11996,47 @@
     <row r="47">
       <c r="A47" s="24" t="inlineStr">
         <is>
-          <t>RC-EML-01</t>
+          <t>AE.34</t>
         </is>
       </c>
       <c r="B47" s="24" t="inlineStr">
         <is>
-          <t>Sender and footer of the e-mails</t>
+          <t>Hold cover rejected by the insurer</t>
         </is>
       </c>
       <c r="C47" s="24" t="inlineStr">
         <is>
-          <t>BRRN.010</t>
+          <t>BRRN.042</t>
         </is>
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>Annex AE</t>
+          <t>Annex AE; FRRN.037.02</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>The sender address of each environment and the standard footer or disclaimer of BDOI e-mails.</t>
+          <t>Approve the wording, the trigger and the recipients. Subject: &lt;renewal reference&gt;: hold cover rejected by &lt;insurer&gt;. Text: &lt;insurer's remarks&gt;, or Rejected by the insurer</t>
         </is>
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>Address per environment; footer text</t>
+          <t>Approve, or the new wording</t>
         </is>
       </c>
       <c r="G47" s="24" t="inlineStr">
         <is>
-          <t>renewals@ (domain of BDOI)</t>
+          <t>Approved</t>
         </is>
       </c>
       <c r="H47" s="24" t="inlineStr">
         <is>
-          <t>BDOI IT</t>
+          <t>Product Owner, Renewal</t>
         </is>
       </c>
       <c r="I47" s="24" t="inlineStr">
         <is>
-          <t>16-Jul-2027</t>
+          <t>30-Nov-2026</t>
         </is>
       </c>
       <c r="J47" s="24" t="inlineStr"/>
@@ -12046,8 +12046,591 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>AE.35</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>Hold cover and placement files to the insurer</t>
+        </is>
+      </c>
+      <c r="C48" s="22" t="inlineStr">
+        <is>
+          <t>BRRN.042; BRRN.040</t>
+        </is>
+      </c>
+      <c r="D48" s="22" t="inlineStr">
+        <is>
+          <t>Annex AE; FRRN.036.06; FRRN.29.04</t>
+        </is>
+      </c>
+      <c r="E48" s="22" t="inlineStr">
+        <is>
+          <t>Approve the wording, the trigger and the recipients. Subject: &lt;document type&gt; - &lt;file name&gt;. Text: Please find attached &lt;file name&gt;.</t>
+        </is>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>Approve, or the new wording</t>
+        </is>
+      </c>
+      <c r="G48" s="22" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H48" s="22" t="inlineStr">
+        <is>
+          <t>Product Owner, Renewal</t>
+        </is>
+      </c>
+      <c r="I48" s="22" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J48" s="22" t="inlineStr"/>
+      <c r="K48" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>AE.36</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>Placement not sent</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>BRRN.040</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>Annex AE; FRRN.29.04</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>Approve the wording, the trigger and the recipients. Subject: &lt;renewal reference&gt; placement not sent. Text: Check the Channel Monitor</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>Approve, or the new wording</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>Product Owner, Renewal</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J49" s="24" t="inlineStr"/>
+      <c r="K49" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>AE.37</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>Placement response received</t>
+        </is>
+      </c>
+      <c r="C50" s="22" t="inlineStr">
+        <is>
+          <t>BRRN.040</t>
+        </is>
+      </c>
+      <c r="D50" s="22" t="inlineStr">
+        <is>
+          <t>Annex AE; FRRN.030.01</t>
+        </is>
+      </c>
+      <c r="E50" s="22" t="inlineStr">
+        <is>
+          <t>Approve the wording, the trigger and the recipients. Subject: &lt;renewal reference&gt; placement approved, or placement rejected. Text: &lt;reason of the rejection&gt;</t>
+        </is>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>Approve, or the new wording</t>
+        </is>
+      </c>
+      <c r="G50" s="22" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H50" s="22" t="inlineStr">
+        <is>
+          <t>Product Owner, Renewal</t>
+        </is>
+      </c>
+      <c r="I50" s="22" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J50" s="22" t="inlineStr"/>
+      <c r="K50" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>AE.38</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>Account submitted for posting</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>BRD 1.008.3</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>Annex AE; FRRN.016.01</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>Approve the wording, the trigger and the recipients. Subject: &lt;renewal reference&gt; submitted for posting. Text: Approve the posting of the renewal of &lt;client&gt;</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Approve, or the new wording</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>Product Owner, Renewal</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J51" s="24" t="inlineStr"/>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>AE.39</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>Transfer request received</t>
+        </is>
+      </c>
+      <c r="C52" s="22" t="inlineStr">
+        <is>
+          <t>BRD 1.006.5; 1.007.1</t>
+        </is>
+      </c>
+      <c r="D52" s="22" t="inlineStr">
+        <is>
+          <t>Annex AE; FRRN.011.01; FRRN.011.05</t>
+        </is>
+      </c>
+      <c r="E52" s="22" t="inlineStr">
+        <is>
+          <t>Approve the wording, the trigger and the recipients. Subject: &lt;transfer request number&gt;: transfer request for a New Business opportunity. Text: Review the transfer request of &lt;client&gt; from &lt;unit&gt;: &lt;justification&gt;</t>
+        </is>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>Approve, or the new wording</t>
+        </is>
+      </c>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H52" s="22" t="inlineStr">
+        <is>
+          <t>Product Owner, Renewal</t>
+        </is>
+      </c>
+      <c r="I52" s="22" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J52" s="22" t="inlineStr"/>
+      <c r="K52" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>AE.40</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>Transfer request decided</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>BRD 1.007.4, 1.007.5</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>Annex AE; FRRN.011.05</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>Approve the wording, the trigger and the recipients. Subject: &lt;transfer request number&gt;: &lt;Accepted, Rejected or Returned for Clarification&gt;. Text: Transfer request of &lt;renewal reference&gt; to &lt;unit&gt;: &lt;outcome&gt; - &lt;remarks&gt;</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>Approve, or the new wording</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
+        <is>
+          <t>Product Owner, Renewal</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J53" s="24" t="inlineStr"/>
+      <c r="K53" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>AE.41</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>Direct-to-Insurer Payment to approve</t>
+        </is>
+      </c>
+      <c r="C54" s="22" t="inlineStr">
+        <is>
+          <t>BRRN.040</t>
+        </is>
+      </c>
+      <c r="D54" s="22" t="inlineStr">
+        <is>
+          <t>Annex AE; FRRN.014.05</t>
+        </is>
+      </c>
+      <c r="E54" s="22" t="inlineStr">
+        <is>
+          <t>Approve the wording, the trigger and the recipients. Subject: &lt;renewal reference&gt;: Direct-to-Insurer Payment to approve. Text: &lt;client&gt;</t>
+        </is>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>Approve, or the new wording</t>
+        </is>
+      </c>
+      <c r="G54" s="22" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H54" s="22" t="inlineStr">
+        <is>
+          <t>Product Owner, Renewal</t>
+        </is>
+      </c>
+      <c r="I54" s="22" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J54" s="22" t="inlineStr"/>
+      <c r="K54" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>AE.42</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>Direct-to-Insurer Payment decided</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>BRRN.040</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>Annex AE; FRRN.014.05</t>
+        </is>
+      </c>
+      <c r="E55" s="24" t="inlineStr">
+        <is>
+          <t>Approve the wording, the trigger and the recipients. Subject: &lt;renewal reference&gt;: Direct-to-Insurer Payment approved, or rejected. Text: &lt;rejection reason&gt;</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>Approve, or the new wording</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H55" s="24" t="inlineStr">
+        <is>
+          <t>Product Owner, Renewal</t>
+        </is>
+      </c>
+      <c r="I55" s="24" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J55" s="24" t="inlineStr"/>
+      <c r="K55" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>AE.43</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>Account returned for correction</t>
+        </is>
+      </c>
+      <c r="C56" s="22" t="inlineStr">
+        <is>
+          <t>BRRN.038</t>
+        </is>
+      </c>
+      <c r="D56" s="22" t="inlineStr">
+        <is>
+          <t>Annex AE; FRRN.26.01</t>
+        </is>
+      </c>
+      <c r="E56" s="22" t="inlineStr">
+        <is>
+          <t>Approve the wording, the trigger and the recipients. Subject: &lt;renewal reference&gt; returned for correction. Text: &lt;reason of the return&gt;</t>
+        </is>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t>Approve, or the new wording</t>
+        </is>
+      </c>
+      <c r="G56" s="22" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H56" s="22" t="inlineStr">
+        <is>
+          <t>Product Owner, Renewal</t>
+        </is>
+      </c>
+      <c r="I56" s="22" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J56" s="22" t="inlineStr"/>
+      <c r="K56" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>AE.44</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>TSU request to approve, assigned and updated</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>BRRN.033</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>Annex AE; FRRN.018.01</t>
+        </is>
+      </c>
+      <c r="E57" s="24" t="inlineStr">
+        <is>
+          <t>Approve the wording, the trigger and the recipients. Subject: &lt;request number&gt; pending your approval; &lt;request number&gt; assigned to you; &lt;request number&gt;: &lt;Approved, Rejected or Returned&gt;, For TSU Processing, comparative table updated, proposal completed by TSU. Text: &lt;client&gt;</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>Approve, or the new wording</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="H57" s="24" t="inlineStr">
+        <is>
+          <t>Product Owner, Renewal</t>
+        </is>
+      </c>
+      <c r="I57" s="24" t="inlineStr">
+        <is>
+          <t>30-Nov-2026</t>
+        </is>
+      </c>
+      <c r="J57" s="24" t="inlineStr"/>
+      <c r="K57" s="24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>RC-EML-01</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>Sender and footer of the e-mails</t>
+        </is>
+      </c>
+      <c r="C58" s="22" t="inlineStr">
+        <is>
+          <t>BRRN.010</t>
+        </is>
+      </c>
+      <c r="D58" s="22" t="inlineStr">
+        <is>
+          <t>Annex AE</t>
+        </is>
+      </c>
+      <c r="E58" s="22" t="inlineStr">
+        <is>
+          <t>The sender address of each environment and the standard footer or disclaimer of BDOI e-mails.</t>
+        </is>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>Address per environment; footer text</t>
+        </is>
+      </c>
+      <c r="G58" s="22" t="inlineStr">
+        <is>
+          <t>renewals@ (domain of BDOI)</t>
+        </is>
+      </c>
+      <c r="H58" s="22" t="inlineStr">
+        <is>
+          <t>BDOI IT</t>
+        </is>
+      </c>
+      <c r="I58" s="22" t="inlineStr">
+        <is>
+          <t>16-Jul-2027</t>
+        </is>
+      </c>
+      <c r="J58" s="22" t="inlineStr"/>
+      <c r="K58" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A12:K47"/>
+  <autoFilter ref="A12:K58"/>
   <mergeCells count="5">
     <mergeCell ref="B4:K4"/>
     <mergeCell ref="B6:K6"/>
@@ -12056,7 +12639,7 @@
     <mergeCell ref="B5:K5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="K14:K347" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
+    <dataValidation sqref="K14:K358" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Status" error="Choose a value from the list (Status)." type="list">
       <formula1>'Lists'!$B$2:$B$4</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_Inputs_BRD-06_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_Inputs_BRD-06_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -816,7 +816,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_Inputs_BRD-06_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_Inputs_BRD-06_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -761,7 +761,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BRD-06 Renewal - what the Business Unit provides for the FRS v1.1</t>
+          <t>BRD-06 Renewal - what the Business Unit provides for the FRS v1.2</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Approvers and users per role' the FRS v1.1 needs from the Business Unit.</t>
+          <t>Items of the kind 'Approvers and users per role' the FRS v1.2 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Integration inputs (BDOI IT)' the FRS v1.1 needs from the Business Unit.</t>
+          <t>Items of the kind 'Integration inputs (BDOI IT)' the FRS v1.2 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -2516,7 +2516,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -3464,7 +3464,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Open decisions' the FRS v1.1 needs from the Business Unit.</t>
+          <t>Items of the kind 'Open decisions' the FRS v1.2 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -5042,7 +5042,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Any question or comment of the Business Unit on the items or on the FRS v1.1.</t>
+          <t>Any question or comment of the Business Unit on the items or on the FRS v1.2.</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr"/>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr"/>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr"/>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="C50" s="14" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr"/>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr"/>
@@ -6666,7 +6666,7 @@
       </c>
       <c r="C72" s="14" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr"/>
@@ -6868,7 +6868,7 @@
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr"/>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr"/>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr"/>
@@ -8119,7 +8119,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Documents and print formats' the FRS v1.1 needs from the Business Unit.</t>
+          <t>Items of the kind 'Documents and print formats' the FRS v1.2 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -9850,7 +9850,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'E-mail wordings' the FRS v1.1 needs from the Business Unit.</t>
+          <t>Items of the kind 'E-mail wordings' the FRS v1.2 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -10091,7 +10091,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Schedules and timings' the FRS v1.1 needs from the Business Unit.</t>
+          <t>Items of the kind 'Schedules and timings' the FRS v1.2 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -12935,7 +12935,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Parameters and thresholds' the FRS v1.1 needs from the Business Unit.</t>
+          <t>Items of the kind 'Parameters and thresholds' the FRS v1.2 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -13977,7 +13977,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -15361,7 +15361,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Lists of values' the FRS v1.1 needs from the Business Unit.</t>
+          <t>Items of the kind 'Lists of values' the FRS v1.2 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -15602,7 +15602,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">
@@ -16403,7 +16403,7 @@
       </c>
       <c r="B2" s="27" t="inlineStr">
         <is>
-          <t>Items of the kind 'Master and reference data' the FRS v1.1 needs from the Business Unit.</t>
+          <t>Items of the kind 'Master and reference data' the FRS v1.2 needs from the Business Unit.</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16644,7 @@
       </c>
       <c r="D11" s="29" t="inlineStr">
         <is>
-          <t>FR item or annex of the FRS v1.1</t>
+          <t>FR item or annex of the FRS v1.2</t>
         </is>
       </c>
       <c r="E11" s="29" t="inlineStr">

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_Inputs_BRD-06_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_Inputs_BRD-06_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -727,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B4:E35"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -737,13 +737,16 @@
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1"/>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1">
       <c r="B4" s="1" t="n"/>
       <c r="C4" s="1" t="n"/>
       <c r="D4" s="1" t="n"/>
       <c r="E4" s="1" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="2" t="inlineStr">
         <is>
@@ -772,6 +775,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="6" t="inlineStr">
         <is>
@@ -844,6 +848,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="9" t="inlineStr">
         <is>
@@ -1046,6 +1051,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
       <c r="B33" s="15" t="inlineStr">
         <is>
@@ -1053,6 +1059,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="26" customHeight="1">
       <c r="B35" s="16" t="inlineStr">
         <is>
@@ -1179,6 +1186,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -2327,6 +2335,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -3516,6 +3525,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -5094,6 +5104,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -5441,6 +5452,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -7587,6 +7599,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="21" t="inlineStr">
         <is>
@@ -8171,6 +8184,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -9902,6 +9916,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -12746,6 +12761,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -13788,6 +13804,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -14096,7 +14113,7 @@
       </c>
       <c r="E13" s="30" t="inlineStr">
         <is>
-          <t>Confirm the value of lead days of the daily extraction. As delivered: 140 days; per market segment if given.</t>
+          <t>Confirm the value of lead days of the daily extraction. By default: 140 days; per market segment if given.</t>
         </is>
       </c>
       <c r="F13" s="30" t="inlineStr">
@@ -14153,7 +14170,7 @@
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Confirm the value of lead days of the daily extraction. As delivered: 140 days; per market segment if given.</t>
+          <t>Confirm the value of lead days of the daily extraction. By default: 140 days; per market segment if given.</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -14206,7 +14223,7 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>Confirm the value of go-live take-over window. As delivered: From go-live to 31-May-2028; urgent up to 31-Jan-2028.</t>
+          <t>Confirm the value of go-live take-over window. By default: From go-live to 31-May-2028; urgent up to 31-Jan-2028.</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
@@ -14259,7 +14276,7 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>Confirm the value of segments initiated in bulk. As delivered: CLG.</t>
+          <t>Confirm the value of segments initiated in bulk. By default: CLG.</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -14312,7 +14329,7 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>Confirm the value of tsi threshold. As delivered: PHP 250,000,000.00.</t>
+          <t>Confirm the value of tsi threshold. By default: PHP 250,000,000.00.</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -14365,7 +14382,7 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>Confirm the value of outstanding premium threshold. As delivered: PHP 0.00 (any balance).</t>
+          <t>Confirm the value of outstanding premium threshold. By default: PHP 0.00 (any balance).</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -14418,7 +14435,7 @@
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>Confirm the value of financial-impact tolerance. As delivered: PHP 0.00 (any change).</t>
+          <t>Confirm the value of financial-impact tolerance. By default: PHP 0.00 (any change).</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -14471,7 +14488,7 @@
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>Confirm the value of renewal advice first and last notice. As delivered: 75 and 45 days before expiry (Annex M).</t>
+          <t>Confirm the value of renewal advice first and last notice. By default: 75 and 45 days before expiry (Annex M).</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -14524,7 +14541,7 @@
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>Confirm the value of late renewal advice warning. As delivered: Less than 30 days before expiry.</t>
+          <t>Confirm the value of late renewal advice warning. By default: Less than 30 days before expiry.</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
@@ -14577,7 +14594,7 @@
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Confirm the value of nrns reminder checkpoint. As delivered: 75 days before expiry (Annex M).</t>
+          <t>Confirm the value of nrns reminder checkpoint. By default: 75 days before expiry (Annex M).</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -14630,7 +14647,7 @@
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>Confirm the value of nrns waiting days after the effective expiry date. As delivered: 0 days, per segment.</t>
+          <t>Confirm the value of nrns waiting days after the effective expiry date. By default: 0 days, per segment.</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -14683,7 +14700,7 @@
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>Confirm the value of non-acceptance letter. As delivered: On the effective expiry date (0 days).</t>
+          <t>Confirm the value of non-acceptance letter. By default: On the effective expiry date (0 days).</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -14736,7 +14753,7 @@
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>Confirm the value of no advice letter / non-renewal letter. As delivered: 1 day after expiry; Non-CBG Non-Renewal Letter 3 days (Annex M).</t>
+          <t>Confirm the value of no advice letter / non-renewal letter. By default: 1 day after expiry; Non-CBG Non-Renewal Letter 3 days (Annex M).</t>
         </is>
       </c>
       <c r="F25" s="24" t="inlineStr">
@@ -14789,7 +14806,7 @@
       </c>
       <c r="E26" s="22" t="inlineStr">
         <is>
-          <t>Confirm the value of re-open of not for renewal. As delivered: Until the expiry date plus 30 days.</t>
+          <t>Confirm the value of re-open of not for renewal. By default: Until the expiry date plus 30 days.</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -14842,7 +14859,7 @@
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>Confirm the value of exception ageing alert. As delivered: 5 working days.</t>
+          <t>Confirm the value of exception ageing alert. By default: 5 working days.</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
@@ -14895,7 +14912,7 @@
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
-          <t>Confirm the value of attention flag (ageing) of the listing. As delivered: IBG 60, Leasing 60, others 30 days before expiry.</t>
+          <t>Confirm the value of attention flag (ageing) of the listing. By default: IBG 60, Leasing 60, others 30 days before expiry.</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -14948,7 +14965,7 @@
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>Confirm the value of insurer reply days. As delivered: 10 days after sending.</t>
+          <t>Confirm the value of insurer reply days. By default: 10 days after sending.</t>
         </is>
       </c>
       <c r="F29" s="24" t="inlineStr">
@@ -15001,7 +15018,7 @@
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
-          <t>Confirm the value of hold cover durations. As delivered: Non-CBG 30, CBG 90; transferred CBG Home 30, CBG Motor 60 days (FRRN.036.01).</t>
+          <t>Confirm the value of hold cover durations. By default: Non-CBG 30, CBG 90; transferred CBG Home 30, CBG Motor 60 days (FRRN.036.01).</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -15054,7 +15071,7 @@
       </c>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>Confirm the value of placement turnaround time. As delivered: 3 business days packaged, 10 non-package; cut-off 3 PM (FRRN.29.05).</t>
+          <t>Confirm the value of placement turnaround time. By default: 3 business days packaged, 10 non-package; cut-off 3 PM (FRRN.29.05).</t>
         </is>
       </c>
       <c r="F31" s="24" t="inlineStr">
@@ -15107,7 +15124,7 @@
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
-          <t>Confirm the value of inactivity warning and session end. As delivered: 15 and 30 minutes.</t>
+          <t>Confirm the value of inactivity warning and session end. By default: 15 and 30 minutes.</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -15160,7 +15177,7 @@
       </c>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>Confirm the value of lines excluded from renewal. As delivered: HMO, group life, group personal accident (Employee Benefits).</t>
+          <t>Confirm the value of lines excluded from renewal. By default: HMO, group life, group personal accident (Employee Benefits).</t>
         </is>
       </c>
       <c r="F33" s="24" t="inlineStr">
@@ -15413,6 +15430,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>
@@ -15721,7 +15739,7 @@
       </c>
       <c r="E13" s="30" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list Renewal dispositions (as delivered: For Renewal; Not for Renewal; For Quotation; For Proposal; Lost Business (labels maintained; the values drive the workflow)). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list Renewal dispositions (default: For Renewal; Not for Renewal; For Quotation; For Proposal; Lost Business (labels maintained; the values drive the workflow)). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F13" s="30" t="inlineStr">
@@ -15778,7 +15796,7 @@
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list Renewal dispositions (as delivered: For Renewal; Not for Renewal; For Quotation; For Proposal; Lost Business (labels maintained; the values drive the workflow)). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list Renewal dispositions (default: For Renewal; Not for Renewal; For Quotation; For Proposal; Lost Business (labels maintained; the values drive the workflow)). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -15831,7 +15849,7 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list Non-renewal reasons (as delivered: The ten reasons of the BRD and the eleven of FRRN.014.02). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list Non-renewal reasons (default: The ten reasons of the BRD and the eleven of FRRN.014.02). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
@@ -15884,7 +15902,7 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list Return reasons (as delivered: The 39 reasons of Annex V and Disapproved). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list Return reasons (default: The 39 reasons of Annex V and Disapproved). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -15937,7 +15955,7 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list Transfer reasons (as delivered: To be given by BDOI (requirements collection workbook)). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list Transfer reasons (default: To be given by BDOI (requirements collection workbook)). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -15990,7 +16008,7 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list Follow-up channels and outcomes (as delivered: Call, E-mail, SMS; outcomes to be given by BDOI). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list Follow-up channels and outcomes (default: Call, E-mail, SMS; outcomes to be given by BDOI). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -16043,7 +16061,7 @@
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list Override reasons (as delivered: To be given by BDOI). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list Override reasons (default: To be given by BDOI). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F19" s="24" t="inlineStr">
@@ -16096,7 +16114,7 @@
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list Insurer dispositions (as delivered: The nine values of FRRN.013.02, each counted as Approve, Revise or Reject). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list Insurer dispositions (default: The nine values of FRRN.013.02, each counted as Approve, Revise or Reject). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -16149,7 +16167,7 @@
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list Client acceptance statuses (as delivered: Pending Client Response; Accepted; Rejected; Request for Revision; Not Applicable (FRRN.025.01)). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list Client acceptance statuses (default: Pending Client Response; Accepted; Rejected; Request for Revision; Not Applicable (FRRN.025.01)). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F21" s="24" t="inlineStr">
@@ -16202,7 +16220,7 @@
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list Placement rejection reasons (as delivered: The reasons of FRRN.030.01.02). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list Placement rejection reasons (default: The reasons of FRRN.030.01.02). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -16255,7 +16273,7 @@
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list KYC statuses (as delivered: Due; Upcoming; Not Required; Pending Follow-Up; Completed (FRRN.039.02)). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list KYC statuses (default: Due; Upcoming; Not Required; Pending Follow-Up; Completed (FRRN.039.02)). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F23" s="24" t="inlineStr">
@@ -16308,7 +16326,7 @@
       </c>
       <c r="E24" s="22" t="inlineStr">
         <is>
-          <t>Give or confirm the values of the list Document types of Renewal (as delivered: RA acceptance; signed Renewal Advice; LAMD report; insurer disposition file; renewal letter; Renewal Advice). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
+          <t>Give or confirm the values of the list Document types of Renewal (default: RA acceptance; signed Renewal Advice; LAMD report; insurer disposition file; renewal letter; Renewal Advice). Template: tab R01 Lists of values and MIS values of the Master Data and Configuration Upload Templates v1.2.</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -16455,6 +16473,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8" ht="24" customHeight="1">
       <c r="A8" s="28" t="inlineStr">
         <is>

--- a/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_Inputs_BRD-06_Business_Unit_Requirements_Collection_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/BDOI_Template_FRS/BRD-06_Renewal/BIBS_Inputs_BRD-06_Business_Unit_Requirements_Collection_v1.0.xlsx
@@ -25,6 +25,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'README'!$A$4:$D$119</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'README'!$4:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Start here'!$A$4:$I$14</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Start here'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Documents and print formats'!$A$12:$K$37</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Documents and print formats'!$12:$12</definedName>
@@ -1086,7 +1087,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -2236,7 +2237,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -3426,7 +3427,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -5009,7 +5010,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -5337,7 +5338,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -5413,7 +5414,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7555,7 +7556,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -8061,6 +8062,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:I14"/>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>
@@ -8085,7 +8087,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -9817,7 +9819,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -12662,7 +12664,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -13705,7 +13707,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -15331,7 +15333,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -16374,7 +16376,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -17682,7 +17684,7 @@
   <pageMargins left="0.4" right="0.4" top="0.6" bottom="0.6" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="1" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
+    <oddHeader>&amp;L&amp;8 &amp;K004EA8Business Unit Requirements Collection&amp;C&amp;8 &amp;K656565&amp;F&amp;R&amp;8 &amp;K656565BDO Insure | BIBS – BDOI Broker System</oddHeader>
     <oddFooter>&amp;L&amp;8 &amp;K656565Confidential – BDOI&amp;C&amp;8 &amp;K656565Page &amp;P of &amp;N&amp;R&amp;8 &amp;K656565Version 1.0</oddFooter>
     <evenHeader/>
     <evenFooter/>
